--- a/NAAD_Safety_Question_Template.xlsx
+++ b/NAAD_Safety_Question_Template.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -172,6 +172,11 @@
       <color rgb="00F57F17"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A3060"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="25">
     <fill>
@@ -296,7 +301,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -362,11 +367,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BDBDBD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BDBDBD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BDBDBD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BDBDBD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -492,6 +511,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1024,7 +1046,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>For VIDEOS only — send via WhatsApp (+233 244977477) or Google Drive (link provided by CMG)</t>
+          <t>For IMAGES — paste a Google Drive share link in the Image URL column of the Questions sheet. For VIDEOS only — send via WhatsApp (+233 244977477) or Google Drive (link provided by CMG)</t>
         </is>
       </c>
       <c r="C12" s="42" t="n"/>
@@ -1292,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:N108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1307,6 +1329,8 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1392,6 +1416,19 @@
 (optional)</t>
         </is>
       </c>
+      <c r="M2" s="45" t="inlineStr">
+        <is>
+          <t>Image URL
+(optional — paste Google Drive share link
+if question has an image)</t>
+        </is>
+      </c>
+      <c r="N2" s="45" t="inlineStr">
+        <is>
+          <t>Image Label / Caption
+(optional — describe the image)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="65" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
@@ -1448,6 +1485,8 @@
         </is>
       </c>
       <c r="L3" s="15" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4" ht="65" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -1504,6 +1543,8 @@
         </is>
       </c>
       <c r="L4" s="16" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5" ht="65" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
@@ -1560,6 +1601,8 @@
         </is>
       </c>
       <c r="L5" s="15" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6" ht="65" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
@@ -1616,6 +1659,8 @@
         </is>
       </c>
       <c r="L6" s="16" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
@@ -1672,6 +1717,8 @@
         </is>
       </c>
       <c r="L7" s="15" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8" ht="65" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -1728,6 +1775,8 @@
         </is>
       </c>
       <c r="L8" s="16" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="17" t="inlineStr"/>
@@ -3131,7 +3180,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="A9:A108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the dropdown list" prompt="Click to select from list" type="list">
